--- a/path2shock_calculation/output/path2shock_Up.xlsx
+++ b/path2shock_calculation/output/path2shock_Up.xlsx
@@ -693,12 +693,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13% max</t>
+          <t>(+13 ppts)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>(+972 ppts)</t>
+          <t>972.0% max</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -721,12 +721,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>13 peak</t>
+          <t>(+13 ppts)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>(+990 ppts)</t>
+          <t>990.0 peak</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -749,12 +749,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>(+100800 bps)</t>
+          <t>1008.0 peak</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -777,12 +777,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>(+102600 bps)</t>
+          <t>1026.0 peak</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -833,12 +833,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>(+115200 bps)</t>
+          <t>1152.0 peak</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -861,12 +861,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>(+117000 bps)</t>
+          <t>1170.0 peak</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -889,12 +889,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>(+118800 bps)</t>
+          <t>1188.0 peak</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -939,12 +939,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>13% peak</t>
+          <t>(+1300 bps)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(+122400 bps)</t>
+          <t>1224.0 peak</t>
         </is>
       </c>
       <c r="E21" t="n">

--- a/path2shock_calculation/output/path2shock_Up.xlsx
+++ b/path2shock_calculation/output/path2shock_Up.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(+13 ppts)</t>
+          <t>(+13.0 ppts)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -721,19 +721,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(+13 ppts)</t>
+          <t>(+3 ppts)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>990.0 peak</t>
+          <t>977.300000000001 peak</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>2.600000000000932</v>
       </c>
       <c r="F13" t="n">
-        <v>990</v>
+        <v>977.300000000001</v>
       </c>
     </row>
     <row r="14">

--- a/path2shock_calculation/output/path2shock_Up.xlsx
+++ b/path2shock_calculation/output/path2shock_Up.xlsx
@@ -473,12 +473,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.5%*</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.001283697047496757</v>
+        <v>0.005121672511340991</v>
       </c>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.5%+</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.001254705144291046</v>
+        <v>0.005018820577164407</v>
       </c>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -517,12 +517,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.5%+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.001226993865030668</v>
+        <v>0.004907975460122671</v>
       </c>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>1.6%#</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>0.001200480192076858</v>
+        <v>0.01560624249699871</v>
       </c>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>1.5%#</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>0.001175088131609936</v>
+        <v>0.01527614571092828</v>
       </c>
       <c r="F6" t="inlineStr"/>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.5%*</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>0.00115074798619097</v>
+        <v>0.004592446716941034</v>
       </c>
       <c r="F7" t="inlineStr"/>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.4%*</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>0.001127395715896373</v>
+        <v>0.004499460343128092</v>
       </c>
       <c r="F8" t="inlineStr"/>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.4%*</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>0.001104972375690627</v>
+        <v>0.004410164773383407</v>
       </c>
       <c r="F9" t="inlineStr"/>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.4%*</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>0.001083423618634782</v>
+        <v>0.004324344540398206</v>
       </c>
       <c r="F10" t="inlineStr"/>
     </row>
@@ -833,19 +833,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1152.0 peak</t>
+          <t>1140.0 trough</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1152</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="18">
@@ -861,19 +861,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1170.0 peak</t>
+          <t>1158.0 trough</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1170</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="19">
@@ -889,19 +889,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1188.0 peak</t>
+          <t>1176.0 trough</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1188</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="20">
@@ -917,12 +917,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.1 %</t>
+          <t>0.3%*</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>0.0008382229673093988</v>
+        <v>0.00334728971072551</v>
       </c>
       <c r="F20" t="inlineStr"/>
     </row>
@@ -939,19 +939,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(+1300 bps)</t>
+          <t>(100 bps)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1224.0 peak</t>
+          <t>1212.0 trough</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1224</v>
+        <v>1212</v>
       </c>
     </row>
   </sheetData>
